--- a/data/administracion_de_tribunales/OP_148_SoliGrupEdad.xlsx
+++ b/data/administracion_de_tribunales/OP_148_SoliGrupEdad.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.hernandez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782F101C-349F-4D77-A86E-921C931ED71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="828" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="4" r:id="rId1"/>
@@ -17,18 +18,30 @@
     <sheet name="2022-2023" sheetId="2" r:id="rId3"/>
     <sheet name="2023-2024" sheetId="3" r:id="rId4"/>
     <sheet name="2024-2025" sheetId="5" r:id="rId5"/>
+    <sheet name="2025-2026" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="23">
   <si>
     <t>Región</t>
   </si>
@@ -102,7 +115,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -139,12 +152,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,17 +435,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,232 +473,197 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>12</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>8</v>
       </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>15</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>9</v>
       </c>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>35</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>25</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4">
-        <v>5</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>24</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>9</v>
       </c>
-      <c r="D6" s="4">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4">
-        <v>2</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="4">
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>24</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>17</v>
       </c>
-      <c r="D7" s="4">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="D7" s="2">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
-        <v>5</v>
-      </c>
-      <c r="D8" s="4">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4">
-        <v>2</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B12">
@@ -730,14 +706,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -765,10 +741,9 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
@@ -787,8 +762,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3">
@@ -801,8 +776,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
@@ -821,8 +796,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5">
@@ -850,8 +825,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6">
@@ -879,8 +854,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7">
@@ -905,8 +880,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8">
@@ -925,8 +900,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9">
@@ -942,8 +917,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10">
@@ -962,8 +937,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11">
@@ -979,8 +954,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12">
@@ -1002,8 +977,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13">
@@ -1031,8 +1006,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14">
@@ -1045,8 +1020,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B15">
@@ -1089,19 +1064,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1129,10 +1104,9 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
@@ -1148,8 +1122,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3">
@@ -1165,8 +1139,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
@@ -1182,8 +1156,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5">
@@ -1205,8 +1179,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6">
@@ -1228,8 +1202,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7">
@@ -1248,8 +1222,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8">
@@ -1268,8 +1242,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9">
@@ -1288,8 +1262,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10">
@@ -1305,8 +1279,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11">
@@ -1319,8 +1293,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12">
@@ -1345,8 +1319,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13">
@@ -1374,8 +1348,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14">
@@ -1394,8 +1368,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B15">
@@ -1427,7 +1401,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
+        <f>SUM(I2:I14)</f>
         <v>19</v>
       </c>
     </row>
@@ -1438,17 +1412,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1476,10 +1450,9 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
@@ -1501,8 +1474,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3">
@@ -1518,8 +1491,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
@@ -1544,8 +1517,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5">
@@ -1567,8 +1540,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6">
@@ -1593,8 +1566,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7">
@@ -1619,8 +1592,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8">
@@ -1642,8 +1615,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9">
@@ -1665,8 +1638,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10">
@@ -1688,8 +1661,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11">
@@ -1699,8 +1672,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12">
@@ -1722,8 +1695,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13">
@@ -1751,8 +1724,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14">
@@ -1774,8 +1747,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B15">
@@ -1818,17 +1791,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1856,253 +1829,879 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
+        <v>21</v>
+      </c>
+      <c r="C2">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>46</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <f>SUM(B2:B14)</f>
+        <v>372</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:I15" si="0">SUM(C2:C14)</f>
+        <v>184</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1059F832-9001-4326-A090-06FDFACC142E}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
         <v>14</v>
       </c>
       <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <f>SUM(B2:B14)</f>
+        <v>179</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:I15" si="0">SUM(C2:C14)</f>
+        <v>108</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B6">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
         <v>15</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15">
-        <v>109</v>
-      </c>
-      <c r="C15">
-        <v>44</v>
-      </c>
-      <c r="D15">
-        <v>11</v>
-      </c>
-      <c r="E15">
-        <v>11</v>
-      </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-      <c r="I15">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
